--- a/output/graficos_nacionales/plot_nacional_e_medianeta_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_medianeta_a_2021.xlsx
@@ -416,7 +416,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_medianeta_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_medianeta_a_2021.xlsx
@@ -2101,7 +2101,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:46</t>
+    <t xml:space="preserve">2026-09-07 12:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_medianeta_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_medianeta_a_2021.xlsx
@@ -2101,7 +2101,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:52</t>
+    <t xml:space="preserve">2026-09-08 10:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
